--- a/data/valuebets_database_2025-08-04.xlsx
+++ b/data/valuebets_database_2025-08-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>04/08 19:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>60</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45873.08915355406</v>
+        <v>45873.08915355324</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>10/08 13:30</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>55</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45873.08915355406</v>
+        <v>45873.08915355324</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>10/08 18:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>60</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45873.08915355406</v>
+        <v>45873.08915355324</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>08/08 21:30</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>55</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45873.08915355406</v>
+        <v>45873.08915355324</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>10/08 18:00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>50</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45873.08915355406</v>
+        <v>45873.08915355324</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>05/08 17:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>60</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45873.08915355406</v>
+        <v>45873.08915355324</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>10/08 18:15</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>55</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45873.08915355406</v>
+        <v>45873.08915355324</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>10/08 09:30</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>60</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45873.08915355406</v>
+        <v>45873.08915355324</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>11/08 22:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>60</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45873.08915355406</v>
+        <v>45873.08915355324</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>07/08 22:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>55</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45873.08915355406</v>
+        <v>45873.08915355324</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>04/08 15:00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>45</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45873.08915355406</v>
+        <v>45873.08915355324</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>09/08 19:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>50</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45873.08915355406</v>
+        <v>45873.08915355324</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>09/08 15:00</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>45</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45873.08915355406</v>
+        <v>45873.08915355324</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>08/08 10:30</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>60</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45873.08915355406</v>
+        <v>45873.08915355324</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>10/08 00:30</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>45</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45873.08915355406</v>
+        <v>45873.08915355324</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>09/08 00:15</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>50</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45873.08915355406</v>
+        <v>45873.08915355324</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>04/08 15:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>45</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45873.08915355406</v>
+        <v>45873.08915355324</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>10/08 17:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>35</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45873.08915355406</v>
+        <v>45873.08915355324</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>09/08 20:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>40</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45873.08915355406</v>
+        <v>45873.08915355324</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>09/08 10:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>35</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45873.08915355406</v>
+        <v>45873.08915355324</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>12/08 18:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>55</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45873.08915355406</v>
+        <v>45873.08915355324</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>09/08 16:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>35</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45873.08915355406</v>
+        <v>45873.08915355324</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>09/08 21:30</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>35</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45873.08915355406</v>
+        <v>45873.08915355324</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>05/08 00:10</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>5.40</t>
-        </is>
+      <c r="F25" t="n">
+        <v>5.4</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,232 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45873.08915355406</v>
+        <v>45873.08915355324</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Tennis | Moins que 3.5 - break | Alexander </t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Alexander Zverev – Alexei PopyrinATP 1000 Toronto</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Moins que 3.5 - break</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>04/08 23:00</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>58,5%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>+14,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>45873.17849175659</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Independie</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Independiente Del Valle – Mushuc RunaCopa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>13/08 00:30</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+9,86%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45873.17849175659</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Zrinjski M</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Zrinjski Mostar – BreidablikLigue Europa</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>07/08 18:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+9,18%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45873.17849175659</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 1(0:1) | Larne – Sa</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Larne – Santa ClaraEurope. Europa Conférence (Q)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1(0:1)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>07/08 19:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+4,74%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45873.17849175659</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Fenerbahce</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Fenerbahce – AlanyasporSüper Lig</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>09/08 18:30</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+2,52%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45873.17849175659</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-04.xlsx
+++ b/data/valuebets_database_2025-08-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1537,10 +1537,8 @@
           <t>04/08 23:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
+      <c r="F26" t="n">
+        <v>1.95</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1553,7 +1551,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45873.17849175659</v>
+        <v>45873.17849175926</v>
       </c>
     </row>
     <row r="27">
@@ -1582,10 +1580,8 @@
           <t>13/08 00:30</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>60</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1598,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45873.17849175659</v>
+        <v>45873.17849175926</v>
       </c>
     </row>
     <row r="28">
@@ -1627,10 +1623,8 @@
           <t>07/08 18:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>45</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1643,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45873.17849175659</v>
+        <v>45873.17849175926</v>
       </c>
     </row>
     <row r="29">
@@ -1672,10 +1666,8 @@
           <t>07/08 19:00</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>40</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1688,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45873.17849175659</v>
+        <v>45873.17849175926</v>
       </c>
     </row>
     <row r="30">
@@ -1717,10 +1709,8 @@
           <t>09/08 18:30</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>45</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1733,7 +1723,142 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45873.17849175659</v>
+        <v>45873.17849175926</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | St. Patric</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>St. Patricks Athletic – Sligo RoversPremier Division</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>08/08 18:45</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+45,2%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45873.2349153439</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 0.5 | AZ Alkmaar</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AZ Alkmaar – FC VaduzLigue Europa Conférence</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Moins que 0.5</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>07/08 18:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+19,9%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45873.2349153439</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 1 | St Patrick</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>St Patricks Athletic – BesiktasEurope. Europa Conférence (Q)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>07/08 18:45</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>8,83%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+5,91%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45873.2349153439</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-04.xlsx
+++ b/data/valuebets_database_2025-08-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,10 +1752,8 @@
           <t>08/08 18:45</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>60</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45873.2349153439</v>
+        <v>45873.23491534722</v>
       </c>
     </row>
     <row r="32">
@@ -1797,10 +1795,8 @@
           <t>07/08 18:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>55</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1813,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45873.2349153439</v>
+        <v>45873.23491534722</v>
       </c>
     </row>
     <row r="33">
@@ -1842,10 +1838,8 @@
           <t>07/08 18:45</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>12.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>12</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1858,7 +1852,97 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45873.2349153439</v>
+        <v>45873.23491534722</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Rapid Buca</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Rapid Bucarest – FC BotosaniLiga 1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>04/08 18:30</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+35,9%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45873.27916020955</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 8.5 - tir cadré | Santos – J</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Santos – Juventude RSBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Moins que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>04/08 23:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>38,1%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+8,59%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45873.27916020955</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-04.xlsx
+++ b/data/valuebets_database_2025-08-04.xlsx
@@ -1881,10 +1881,8 @@
           <t>04/08 18:30</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>60</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1897,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45873.27916020955</v>
+        <v>45873.27916020833</v>
       </c>
     </row>
     <row r="35">
@@ -1926,10 +1924,8 @@
           <t>04/08 23:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
+      <c r="F35" t="n">
+        <v>2.85</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1942,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45873.27916020955</v>
+        <v>45873.27916020833</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-04.xlsx
+++ b/data/valuebets_database_2025-08-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1941,6 +1941,51 @@
         <v>45873.27916020833</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 11-2- se qualifie | Lech Pozna</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Lech Poznan – Étoile Rouge BelgradeEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>11-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>06/08 18:30</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>34,3%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+2,76%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45873.39943892657</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-04.xlsx
+++ b/data/valuebets_database_2025-08-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1967,10 +1967,8 @@
           <t>06/08 18:30</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>3</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1983,7 +1981,97 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45873.39943892657</v>
+        <v>45873.39943892361</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Gremio – S</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Gremio – Sport RecifeSérie A</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>10/08 23:30</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+2,08%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45873.43605723351</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Trabzonspo</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Trabzonspor – KocaelisporSüper Lig</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>11/08 18:30</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+1,08%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45873.43605723351</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-04.xlsx
+++ b/data/valuebets_database_2025-08-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2010,10 +2010,8 @@
           <t>10/08 23:30</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>50</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2026,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45873.43605723351</v>
+        <v>45873.4360572338</v>
       </c>
     </row>
     <row r="38">
@@ -2055,23 +2053,111 @@
           <t>11/08 18:30</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" t="n">
+        <v>45</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+1,08%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45873.4360572338</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Spartak Tr</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Spartak Trnava – Tatran PresovFortuna Liga</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>10/08 17:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>45.00</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>+1,08%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>45873.43605723351</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+14,0%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45873.47344784273</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Newell's O</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Newell's Old Boys – Central CordobaLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>09/08 00:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+2,04%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45873.47344784273</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-04.xlsx
+++ b/data/valuebets_database_2025-08-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2096,10 +2096,8 @@
           <t>10/08 17:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>45</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2112,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45873.47344784273</v>
+        <v>45873.47344784722</v>
       </c>
     </row>
     <row r="40">
@@ -2141,10 +2139,8 @@
           <t>09/08 00:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>45</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2157,7 +2153,97 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45873.47344784273</v>
+        <v>45873.47344784722</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 9.5 - tir cadré | Santos – J</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Santos – Juventude RSBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Moins que 9.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>04/08 23:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>49,1%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+5,58%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45873.53685327273</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 11-2- se qualifie | Ludogorets</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ludogorets – FerencvarosEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>11-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>06/08 17:30</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>44,0%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+3,29%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45873.53685327273</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-04.xlsx
+++ b/data/valuebets_database_2025-08-04.xlsx
@@ -2182,10 +2182,8 @@
           <t>04/08 23:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="F41" t="n">
+        <v>2.15</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2198,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45873.53685327273</v>
+        <v>45873.53685327547</v>
       </c>
     </row>
     <row r="42">
@@ -2227,10 +2225,8 @@
           <t>06/08 17:30</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="F42" t="n">
+        <v>2.35</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2243,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45873.53685327273</v>
+        <v>45873.53685327547</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-04.xlsx
+++ b/data/valuebets_database_2025-08-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2242,6 +2242,96 @@
         <v>45873.53685327547</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Varazdin –</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Varazdin – HNK GoricaHNL</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>04/08 18:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+43,4%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45873.60279057704</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | PAOK Salon</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>PAOK Salonique – Wolfsberger ACLigue Europa</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>07/08 17:30</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+28,4%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45873.60279057704</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-04.xlsx
+++ b/data/valuebets_database_2025-08-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2268,10 +2268,8 @@
           <t>04/08 18:00</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>60</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2284,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45873.60279057704</v>
+        <v>45873.60279057871</v>
       </c>
     </row>
     <row r="44">
@@ -2313,10 +2311,8 @@
           <t>07/08 17:30</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>60</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2329,7 +2325,97 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45873.60279057704</v>
+        <v>45873.60279057871</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | 11-2- se qualifie | Ludogorets</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ludogorets Razgrad – Ferencvárosi TCEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>11-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>06/08 17:30</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>44,1%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+3,55%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45873.64422387136</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Plus que 6.51er set1er participant | Arevalo M/</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Arevalo M/Pavic M – Salisbury J/Skupski NATP 1000 Toronto - Doubles</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Plus que 6.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>04/08 21:30</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>19,7%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+2,21%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45873.64422387136</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-04.xlsx
+++ b/data/valuebets_database_2025-08-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2354,10 +2354,8 @@
           <t>06/08 17:30</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="F45" t="n">
+        <v>2.35</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2370,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45873.64422387136</v>
+        <v>45873.64422386574</v>
       </c>
     </row>
     <row r="46">
@@ -2399,10 +2397,8 @@
           <t>04/08 21:30</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>5.20</t>
-        </is>
+      <c r="F46" t="n">
+        <v>5.2</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2415,7 +2411,97 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45873.64422387136</v>
+        <v>45873.64422386574</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 2 | Paide Linn</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Paide Linnameeskond – JK Tallinna KalevEstonie. Estonie - Premier League</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>09/08 16:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+51,1%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45873.68957505294</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | FC Inter T</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>FC Inter Turku – AC OuluVeikkausliiga</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>08/08 15:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+19,4%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45873.68957505294</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-04.xlsx
+++ b/data/valuebets_database_2025-08-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2440,10 +2440,8 @@
           <t>09/08 16:00</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>55</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2456,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45873.68957505294</v>
+        <v>45873.68957505787</v>
       </c>
     </row>
     <row r="48">
@@ -2485,10 +2483,8 @@
           <t>08/08 15:00</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>55</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2501,7 +2497,97 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45873.68957505294</v>
+        <v>45873.68957505787</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 10.5 - tir cadré | Santos – J</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Santos – Juventude RSBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Moins que 10.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>04/08 23:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>60,3%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+5,59%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45873.72679517105</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Plus que 6.51er set1er participant | Alex De Mi</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Alex De Minaur – Ben SheltonATP 1000 Toronto</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Plus que 6.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>05/08 20:30</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>5.40</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>19,3%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+3,98%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45873.72679517105</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-04.xlsx
+++ b/data/valuebets_database_2025-08-04.xlsx
@@ -2526,10 +2526,8 @@
           <t>04/08 23:00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
+      <c r="F49" t="n">
+        <v>1.75</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2542,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45873.72679517105</v>
+        <v>45873.72679517361</v>
       </c>
     </row>
     <row r="50">
@@ -2571,10 +2569,8 @@
           <t>05/08 20:30</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>5.40</t>
-        </is>
+      <c r="F50" t="n">
+        <v>5.4</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2587,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45873.72679517105</v>
+        <v>45873.72679517361</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-04.xlsx
+++ b/data/valuebets_database_2025-08-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2586,6 +2586,141 @@
         <v>45873.72679517361</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | San Lorenz</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>San Lorenzo – Velez SarsfieldLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>07/08 22:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>70.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+31,5%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45873.80706271082</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 11.5 - tirs2e équipe | Santos – J</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Santos – Juventude RSBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Plus que 11.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>04/08 23:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>38,7%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+2,51%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45873.80706271082</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 4.51er set2e participant | Marta Kost</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Marta Kostyuk – Elena RybakinaWTA 1000 Montreal</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Moins que 4.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>04/08 22:00</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>24,3%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+1,97%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45873.80706271082</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-04.xlsx
+++ b/data/valuebets_database_2025-08-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2612,10 +2612,8 @@
           <t>07/08 22:00</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>70.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>70</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2628,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45873.80706271082</v>
+        <v>45873.80706270834</v>
       </c>
     </row>
     <row r="52">
@@ -2657,10 +2655,8 @@
           <t>04/08 23:00</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
+      <c r="F52" t="n">
+        <v>2.65</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2673,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45873.80706271082</v>
+        <v>45873.80706270834</v>
       </c>
     </row>
     <row r="53">
@@ -2702,10 +2698,8 @@
           <t>04/08 22:00</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="F53" t="n">
+        <v>4.2</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2718,7 +2712,97 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45873.80706271082</v>
+        <v>45873.80706270834</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 21-2- se qualifie | Hamrun Spa</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Hamrun Spartans – Maccabi Tel AvivEurope. Europa League (Q)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>21-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>05/08 17:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>93,4%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+1,79%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45873.85273946586</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 11-2- se qualifie | Malmö – Co</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Malmö – CopenhagueEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>11-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>05/08 17:00</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>36,8%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+1,27%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45873.85273946586</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-04.xlsx
+++ b/data/valuebets_database_2025-08-04.xlsx
@@ -2741,10 +2741,8 @@
           <t>05/08 17:00</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
+      <c r="F54" t="n">
+        <v>1.09</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2757,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45873.85273946586</v>
+        <v>45873.85273946759</v>
       </c>
     </row>
     <row r="55">
@@ -2786,10 +2784,8 @@
           <t>05/08 17:00</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F55" t="n">
+        <v>2.75</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2802,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45873.85273946586</v>
+        <v>45873.85273946759</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-04.xlsx
+++ b/data/valuebets_database_2025-08-04.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2801,6 +2801,51 @@
         <v>45873.85273946759</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Dynamo Kie</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Dynamo Kiev – Pafos FCLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>05/08 18:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+0,32%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45873.97489663908</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
